--- a/MAIN/BOM.xlsx
+++ b/MAIN/BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chand\Localisation in IOT git files\Git_hub_RP\Bluetooth-and-Mioty-Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaure\Documents\GitHub\Bluetooth-and-Mioty-Localization\MAIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799AE4BC-AADB-4287-B8AE-C81CA0FCDB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB1AFB9-2FAC-4D18-96CB-1AF78F27078F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,12 +99,6 @@
     <t>Y3</t>
   </si>
   <si>
-    <t>NT2016SA 52MHz END5225A</t>
-  </si>
-  <si>
-    <t>https://www.digikey.de/en/products/detail/ndk-nihon-dempa-kogyo-co-ltd/NT2016SA-52MHZ-END5225A/9171992?s=N4IgTCBcDaIHIBUwAYCMA2AygQQAQFYwBZACQC9cBROAEULH2xAF0BfIA</t>
-  </si>
-  <si>
     <t>L3</t>
   </si>
   <si>
@@ -427,6 +421,12 @@
   </si>
   <si>
     <t>Blue</t>
+  </si>
+  <si>
+    <t>ECS-1612MV</t>
+  </si>
+  <si>
+    <t>https://www.digikey.at/en/products/detail/ecs-inc/ECS-1612MV-520-CN-TR/22464834</t>
   </si>
 </sst>
 </file>
@@ -768,16 +768,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" customWidth="1"/>
-    <col min="6" max="6" width="138.1796875" customWidth="1"/>
-    <col min="7" max="7" width="28.81640625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="6" width="138.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -800,12 +800,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -819,227 +819,227 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
         <v>108</v>
       </c>
-      <c r="E10" t="s">
-        <v>110</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1047,63 +1047,63 @@
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
       </c>
       <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
         <v>97</v>
       </c>
-      <c r="E21" t="s">
-        <v>99</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2</v>
       </c>
@@ -1131,383 +1131,383 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
       <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
         <v>35</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>37</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
         <v>35</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>37</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
         <v>36</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9</v>
       </c>
       <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
       <c r="F31" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>10</v>
       </c>
       <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" t="s">
         <v>52</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D34" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9</v>
       </c>
       <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
         <v>64</v>
       </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1</v>
       </c>
       <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" t="s">
         <v>88</v>
       </c>
-      <c r="C45" t="s">
+      <c r="E45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1526,24 +1526,23 @@
     <hyperlink ref="F17" r:id="rId12" xr:uid="{E90E8E5D-6049-4E64-A4CC-7A3C38EDE1BD}"/>
     <hyperlink ref="F18" r:id="rId13" xr:uid="{BBE8552D-E013-4A5C-816F-6D9318AEA4EA}"/>
     <hyperlink ref="F21" r:id="rId14" xr:uid="{CDE11C4C-F151-451A-B1BE-4E2FE821BEFA}"/>
-    <hyperlink ref="F24" r:id="rId15" xr:uid="{8E94842A-C938-4B1C-A463-8851C227BA1E}"/>
-    <hyperlink ref="F25" r:id="rId16" xr:uid="{6EF2DEF8-3A9E-4603-B943-6D14C205FA99}"/>
-    <hyperlink ref="F26" r:id="rId17" xr:uid="{2DCBF906-DF54-4368-BC71-B26C97E8F048}"/>
-    <hyperlink ref="F39" r:id="rId18" xr:uid="{44AD2C82-A23C-4467-930A-48D7D3770B50}"/>
-    <hyperlink ref="F30" r:id="rId19" xr:uid="{3D8C70F3-86D1-408F-B991-32BBA9AE0284}"/>
-    <hyperlink ref="F29" r:id="rId20" xr:uid="{B4530D85-708B-4214-B1E4-BAFC599C8674}"/>
-    <hyperlink ref="F27" r:id="rId21" xr:uid="{467D3286-50FF-4216-8937-835A6BA4C3A8}"/>
-    <hyperlink ref="F28" r:id="rId22" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
-    <hyperlink ref="F31" r:id="rId23" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
-    <hyperlink ref="F32" r:id="rId24" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
-    <hyperlink ref="F34" r:id="rId25" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
-    <hyperlink ref="F35" r:id="rId26" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
-    <hyperlink ref="F36" r:id="rId27" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
-    <hyperlink ref="F37" r:id="rId28" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
-    <hyperlink ref="F38" r:id="rId29" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
-    <hyperlink ref="F40" r:id="rId30" xr:uid="{7DC9F4BF-0E00-4FE8-9952-52FD0B31FE2B}"/>
-    <hyperlink ref="F41" r:id="rId31" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
-    <hyperlink ref="F45" r:id="rId32" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
+    <hyperlink ref="F25" r:id="rId15" xr:uid="{6EF2DEF8-3A9E-4603-B943-6D14C205FA99}"/>
+    <hyperlink ref="F26" r:id="rId16" xr:uid="{2DCBF906-DF54-4368-BC71-B26C97E8F048}"/>
+    <hyperlink ref="F39" r:id="rId17" xr:uid="{44AD2C82-A23C-4467-930A-48D7D3770B50}"/>
+    <hyperlink ref="F30" r:id="rId18" xr:uid="{3D8C70F3-86D1-408F-B991-32BBA9AE0284}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{B4530D85-708B-4214-B1E4-BAFC599C8674}"/>
+    <hyperlink ref="F27" r:id="rId20" xr:uid="{467D3286-50FF-4216-8937-835A6BA4C3A8}"/>
+    <hyperlink ref="F28" r:id="rId21" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
+    <hyperlink ref="F31" r:id="rId22" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
+    <hyperlink ref="F32" r:id="rId23" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
+    <hyperlink ref="F34" r:id="rId24" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
+    <hyperlink ref="F35" r:id="rId25" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
+    <hyperlink ref="F36" r:id="rId26" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
+    <hyperlink ref="F37" r:id="rId27" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
+    <hyperlink ref="F38" r:id="rId28" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
+    <hyperlink ref="F40" r:id="rId29" xr:uid="{7DC9F4BF-0E00-4FE8-9952-52FD0B31FE2B}"/>
+    <hyperlink ref="F41" r:id="rId30" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
+    <hyperlink ref="F45" r:id="rId31" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MAIN/BOM.xlsx
+++ b/MAIN/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaure\Documents\GitHub\Bluetooth-and-Mioty-Localization\MAIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB1AFB9-2FAC-4D18-96CB-1AF78F27078F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3DCD9C-5DA3-47D4-AAB0-CD1AF2347D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="173">
   <si>
     <t>S. No.</t>
   </si>
@@ -90,15 +90,6 @@
     <t>Resistor</t>
   </si>
   <si>
-    <t>CRCW02011K00JNED</t>
-  </si>
-  <si>
-    <t>https://www.digikey.de/en/products/detail/vishay-dale/CRCW02011K00JNED/1178450</t>
-  </si>
-  <si>
-    <t>Y3</t>
-  </si>
-  <si>
     <t>L3</t>
   </si>
   <si>
@@ -123,9 +114,6 @@
     <t>C19</t>
   </si>
   <si>
-    <t>C20</t>
-  </si>
-  <si>
     <t>Capacitor</t>
   </si>
   <si>
@@ -252,18 +240,9 @@
     <t>https://www.digikey.de/en/products/detail/murata-electronics/GRM1555C1HR50WA01D/3694056?s=N4IgTCBcDaIOICUCyBGArBgwigEgtADAOoCCBKAIiALoC%2BQA</t>
   </si>
   <si>
-    <t>GRM1555C1H101JA01D</t>
-  </si>
-  <si>
-    <t>100p</t>
-  </si>
-  <si>
     <t>Connector</t>
   </si>
   <si>
-    <t>https://www.digikey.de/en/products/detail/murata-electronics/GRM1555C1H101JA01D/3693829?s=N4IgTCBcDaIOICUCyBGArBgwigEigDCgFICChAIiALoC%2BQA</t>
-  </si>
-  <si>
     <t>3n</t>
   </si>
   <si>
@@ -357,18 +336,9 @@
     <t>https://www.digikey.de/en/products/detail/ecs-inc/ECS-80-12-33-JGN-TR/10478769</t>
   </si>
   <si>
-    <t>GRM1555C1H200JA01D</t>
-  </si>
-  <si>
-    <t>https://www.digikey.de/de/products/detail/murata-electronics/GRM1555C1H200JA01D/3693839?s=N4IgTCBcDaIOICUCyBGArBgwigEmADPgFICC%2BKAIiALoC%2BQA</t>
-  </si>
-  <si>
     <t>32KHz</t>
   </si>
   <si>
-    <t>20p</t>
-  </si>
-  <si>
     <t>C3</t>
   </si>
   <si>
@@ -423,17 +393,164 @@
     <t>Blue</t>
   </si>
   <si>
-    <t>ECS-1612MV</t>
-  </si>
-  <si>
-    <t>https://www.digikey.at/en/products/detail/ecs-inc/ECS-1612MV-520-CN-TR/22464834</t>
+    <t>RB1</t>
+  </si>
+  <si>
+    <t>CRCW040220R0FKED</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/vishay-dale/CRCW040220R0FKED/1177811</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/jauch-quartz/CR2032/13540138</t>
+  </si>
+  <si>
+    <t>14p</t>
+  </si>
+  <si>
+    <t>24p</t>
+  </si>
+  <si>
+    <t>GRM1555C1H240GA01D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/murata-electronics/GRM1555C1H240GA01D/3693952</t>
+  </si>
+  <si>
+    <t>GJM1555C1H140GB01D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/murata-electronics/GJM1555C1H140GB01D/6606072</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>XTAL1</t>
+  </si>
+  <si>
+    <t>CS06016-52M</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/ndk-nihon-dempa-kogyo-co-ltd/CS06016-52M/9172036?srsltid=AfmBOooDpFV9fEmiFrEQiWBEy8DNIl_s4x9r_rX8aBmIivIYiRR3MFMR</t>
+  </si>
+  <si>
+    <t>10p</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/murata-electronics/GRM1555C1H100FA01D/2543854</t>
+  </si>
+  <si>
+    <t>GRM1555C1H100FA01D</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>Accelerometer</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/tdk-invensense/ICM-45686/24374985</t>
+  </si>
+  <si>
+    <t>ICM-45686</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/vishay-dale/CRCW04024K70FKED/1178083</t>
+  </si>
+  <si>
+    <t>CRCW04024K70FKED</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>Magnetometer</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>IIS2MDCTR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/stmicroelectronics/IIS2MDCTR/7927708?s=N4IgTCBcDaIJJwMpgLIBEDCAVASiAugL5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> magnetoresistiv Sensor X, Y, Z Achse 12-LGA (2x2)</t>
+  </si>
+  <si>
+    <t>220u</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>GRM155R61A106ME11D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/murata-electronics/GRM155R61A106ME11D/12091056</t>
+  </si>
+  <si>
+    <t>10u</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/murata-electronics/GRM155R71C224KA12D/2175204</t>
+  </si>
+  <si>
+    <t>GRM155R71C224KA12D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +565,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -471,7 +594,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -486,6 +609,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -767,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="17" customWidth="1"/>
@@ -810,739 +940,1184 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
         <v>99</v>
       </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>6</v>
       </c>
-      <c r="B15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" t="s">
-        <v>125</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>2</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="D18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>2</v>
       </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>16</v>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23">
-        <v>402</v>
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>108</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>30</v>
+        <v>108</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>39</v>
+        <v>108</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>39</v>
+        <v>108</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>140</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>74</v>
+        <v>33</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>83</v>
+        <v>32</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>7</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="4" t="s">
+      <c r="D48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="F49" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>10</v>
       </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>1</v>
       </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" t="s">
+        <v>155</v>
+      </c>
+      <c r="F55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" t="s">
+        <v>113</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" t="s">
+        <v>108</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s">
+        <v>157</v>
+      </c>
+      <c r="F58" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" t="s">
+        <v>157</v>
+      </c>
+      <c r="F59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>6</v>
+      </c>
+      <c r="B60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" t="s">
+        <v>108</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>160</v>
+      </c>
+      <c r="C62" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" t="s">
+        <v>163</v>
+      </c>
+      <c r="F62" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
         <v>87</v>
       </c>
-      <c r="D45" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" t="s">
-        <v>90</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>89</v>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E63" t="s">
+        <v>157</v>
+      </c>
+      <c r="F63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" t="s">
+        <v>157</v>
+      </c>
+      <c r="F64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" t="s">
+        <v>172</v>
+      </c>
+      <c r="F65" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" t="s">
+        <v>170</v>
+      </c>
+      <c r="E66" t="s">
+        <v>168</v>
+      </c>
+      <c r="F66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" t="s">
+        <v>105</v>
+      </c>
+      <c r="E67" t="s">
+        <v>108</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>167</v>
+      </c>
+      <c r="C68" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1" xr:uid="{D50FFC5A-821F-4C94-B04A-F406D35E99DC}"/>
-    <hyperlink ref="F20" r:id="rId2" xr:uid="{3206DE1E-5B1F-4613-AE54-DD3C9A177642}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{E06E345B-93C3-4FA7-935F-638068279AAA}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{B5A236EB-917D-4615-83F0-A079BF0128A0}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{848B4B6B-14A1-48B5-96A9-8F1107784A43}"/>
-    <hyperlink ref="F11" r:id="rId6" xr:uid="{F9107EB9-C9F2-4975-BB00-7BA16E1BD9B9}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{C1C7415B-429D-491B-B931-EE38B7D918E5}"/>
-    <hyperlink ref="F12" r:id="rId8" xr:uid="{956B8FB4-224F-4E3B-92E7-CD01E96D4DAB}"/>
-    <hyperlink ref="F13" r:id="rId9" xr:uid="{4AC738DB-F9CA-435E-9BD3-136B300DF05D}"/>
-    <hyperlink ref="F14" r:id="rId10" xr:uid="{F56DB16A-7315-4DE4-A8FC-9739959F9F5B}"/>
-    <hyperlink ref="F15" r:id="rId11" xr:uid="{53C11F23-7475-46EB-8BBA-D8935F039069}"/>
-    <hyperlink ref="F17" r:id="rId12" xr:uid="{E90E8E5D-6049-4E64-A4CC-7A3C38EDE1BD}"/>
-    <hyperlink ref="F18" r:id="rId13" xr:uid="{BBE8552D-E013-4A5C-816F-6D9318AEA4EA}"/>
-    <hyperlink ref="F21" r:id="rId14" xr:uid="{CDE11C4C-F151-451A-B1BE-4E2FE821BEFA}"/>
-    <hyperlink ref="F25" r:id="rId15" xr:uid="{6EF2DEF8-3A9E-4603-B943-6D14C205FA99}"/>
-    <hyperlink ref="F26" r:id="rId16" xr:uid="{2DCBF906-DF54-4368-BC71-B26C97E8F048}"/>
-    <hyperlink ref="F39" r:id="rId17" xr:uid="{44AD2C82-A23C-4467-930A-48D7D3770B50}"/>
-    <hyperlink ref="F30" r:id="rId18" xr:uid="{3D8C70F3-86D1-408F-B991-32BBA9AE0284}"/>
-    <hyperlink ref="F29" r:id="rId19" xr:uid="{B4530D85-708B-4214-B1E4-BAFC599C8674}"/>
-    <hyperlink ref="F27" r:id="rId20" xr:uid="{467D3286-50FF-4216-8937-835A6BA4C3A8}"/>
-    <hyperlink ref="F28" r:id="rId21" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
-    <hyperlink ref="F31" r:id="rId22" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
-    <hyperlink ref="F32" r:id="rId23" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
-    <hyperlink ref="F34" r:id="rId24" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
-    <hyperlink ref="F35" r:id="rId25" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
-    <hyperlink ref="F36" r:id="rId26" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
-    <hyperlink ref="F37" r:id="rId27" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
-    <hyperlink ref="F38" r:id="rId28" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
-    <hyperlink ref="F40" r:id="rId29" xr:uid="{7DC9F4BF-0E00-4FE8-9952-52FD0B31FE2B}"/>
-    <hyperlink ref="F41" r:id="rId30" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
-    <hyperlink ref="F45" r:id="rId31" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
+    <hyperlink ref="F21" r:id="rId1" xr:uid="{3206DE1E-5B1F-4613-AE54-DD3C9A177642}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{E06E345B-93C3-4FA7-935F-638068279AAA}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{B5A236EB-917D-4615-83F0-A079BF0128A0}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{848B4B6B-14A1-48B5-96A9-8F1107784A43}"/>
+    <hyperlink ref="F12" r:id="rId5" xr:uid="{F9107EB9-C9F2-4975-BB00-7BA16E1BD9B9}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{C1C7415B-429D-491B-B931-EE38B7D918E5}"/>
+    <hyperlink ref="F18" r:id="rId7" xr:uid="{E90E8E5D-6049-4E64-A4CC-7A3C38EDE1BD}"/>
+    <hyperlink ref="F19" r:id="rId8" xr:uid="{BBE8552D-E013-4A5C-816F-6D9318AEA4EA}"/>
+    <hyperlink ref="F22" r:id="rId9" xr:uid="{CDE11C4C-F151-451A-B1BE-4E2FE821BEFA}"/>
+    <hyperlink ref="F33" r:id="rId10" xr:uid="{6EF2DEF8-3A9E-4603-B943-6D14C205FA99}"/>
+    <hyperlink ref="F34" r:id="rId11" xr:uid="{2DCBF906-DF54-4368-BC71-B26C97E8F048}"/>
+    <hyperlink ref="F47" r:id="rId12" xr:uid="{44AD2C82-A23C-4467-930A-48D7D3770B50}"/>
+    <hyperlink ref="F38" r:id="rId13" xr:uid="{3D8C70F3-86D1-408F-B991-32BBA9AE0284}"/>
+    <hyperlink ref="F37" r:id="rId14" xr:uid="{B4530D85-708B-4214-B1E4-BAFC599C8674}"/>
+    <hyperlink ref="F35" r:id="rId15" xr:uid="{467D3286-50FF-4216-8937-835A6BA4C3A8}"/>
+    <hyperlink ref="F36" r:id="rId16" xr:uid="{283DFAF0-B027-460E-BEA3-E28DB7D75637}"/>
+    <hyperlink ref="F39" r:id="rId17" xr:uid="{217435C8-5FF7-4B86-B4E9-BFA135B39084}"/>
+    <hyperlink ref="F40" r:id="rId18" xr:uid="{F9702DF9-CC1B-42B0-96AD-216A11C735E3}"/>
+    <hyperlink ref="F42" r:id="rId19" xr:uid="{A27D8FF2-1762-470C-89EB-CA17719CDF2A}"/>
+    <hyperlink ref="F43" r:id="rId20" xr:uid="{CB456E9B-1680-41E5-A8F6-0AC98E1B2684}"/>
+    <hyperlink ref="F44" r:id="rId21" xr:uid="{84C8FBE4-112A-49FF-8A0D-F9CB3B1FE98A}"/>
+    <hyperlink ref="F45" r:id="rId22" xr:uid="{7AB50742-9609-4684-BB22-23FCC3D0AFAC}"/>
+    <hyperlink ref="F46" r:id="rId23" xr:uid="{CEB15CA5-20DF-48F1-A71E-97BE776E1A3A}"/>
+    <hyperlink ref="F49" r:id="rId24" display="https://www.digikey.de/de/products/detail/te-connectivity-linx/CONMHF1-SMD-G-T/15293397?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20179951824&amp;gbraid=0AAAAADrbLlgcW0wDpxdB3QLoBqEJ77uUK&amp;gclid=Cj0KCQjw6bfHBhDNARIsAIGsqLjLl1jPmqBYngNawJjpDc2NL71_ijr013dRm_6SUY6Z-PSxDqZcU4AaAjl_EALw_wcB" xr:uid="{72808A11-5911-4A58-ADDF-A972CB0F47C2}"/>
+    <hyperlink ref="F53" r:id="rId25" xr:uid="{EBB4519B-B72F-4CC1-9062-C7A3B3B0DDF2}"/>
+    <hyperlink ref="F23" r:id="rId26" xr:uid="{2444E7F9-12BD-42E6-AE3F-D56336F9D828}"/>
+    <hyperlink ref="F24" r:id="rId27" xr:uid="{DADCDF1D-4918-481F-94A3-52B31B5558B5}"/>
+    <hyperlink ref="F25" r:id="rId28" xr:uid="{9C9C4086-80EB-43C3-B1A9-F24609908460}"/>
+    <hyperlink ref="F26" r:id="rId29" xr:uid="{F2D7E8A1-E468-4CBC-93D7-F41721223FCD}"/>
+    <hyperlink ref="F27" r:id="rId30" xr:uid="{9072A8B7-BB60-469A-8C9A-751137450A1E}"/>
+    <hyperlink ref="F28" r:id="rId31" xr:uid="{3F0B231E-8513-40C3-91FD-3A197A6A2489}"/>
+    <hyperlink ref="F56" r:id="rId32" xr:uid="{48C1C764-1533-418B-92FF-0715C755090E}"/>
+    <hyperlink ref="F57" r:id="rId33" xr:uid="{89295D1F-98D7-49F1-8ECD-A63A31CB2E30}"/>
+    <hyperlink ref="F60" r:id="rId34" xr:uid="{0B762A7B-77E3-4020-95E2-B10D2ABA3A5A}"/>
+    <hyperlink ref="F67" r:id="rId35" xr:uid="{83551B11-2746-4512-AE7F-59155A0DC3CB}"/>
+    <hyperlink ref="F68" r:id="rId36" xr:uid="{76CCA5CE-6CE1-43B1-941A-F96B8273F8E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
